--- a/slide_classification/TCGA_Results/Tissue_Type_Clustering/ConchV1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
+++ b/slide_classification/TCGA_Results/Tissue_Type_Clustering/ConchV1/1-MSIH/Output/cross_valid_avg_probs_all.xlsx
@@ -517,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.251322</v>
+        <v>0.376305</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -560,7 +560,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9631110000000001</v>
+        <v>0.969808</v>
       </c>
       <c r="H3" t="n">
         <v>1</v>
@@ -603,7 +603,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.449305</v>
+        <v>0.373113</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -646,7 +646,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5107930000000001</v>
+        <v>0.639282</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -686,10 +686,10 @@
         <v>0.104826</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0.512153</v>
+        <v>0.409503</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -732,7 +732,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.750019</v>
+        <v>0.801962</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.38755</v>
+        <v>0.359381</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -818,7 +818,7 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.249025</v>
+        <v>0.317263</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -858,10 +858,10 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>0.447067</v>
+        <v>0.591863</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -904,7 +904,7 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.339672</v>
+        <v>0.392642</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9572619999999999</v>
+        <v>0.919749</v>
       </c>
       <c r="H12" t="n">
         <v>1</v>
@@ -990,7 +990,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0.932403</v>
+        <v>0.798426</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1033,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.333816</v>
+        <v>0.425128</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1076,7 +1076,7 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.234279</v>
+        <v>0.254218</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.32117</v>
+        <v>0.42395</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.284502</v>
+        <v>0.283822</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.130066</v>
+        <v>0.267373</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.186122</v>
+        <v>0.211618</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.209242</v>
+        <v>0.159311</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.190098</v>
+        <v>0.22808</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1377,7 +1377,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8029539999999999</v>
+        <v>0.642462</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1420,7 +1420,7 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.259305</v>
+        <v>0.33388</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.193715</v>
+        <v>0.295601</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.221424</v>
+        <v>0.181763</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1549,7 +1549,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0.299869</v>
+        <v>0.434599</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>0.261412</v>
+        <v>0.41336</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1632,10 +1632,10 @@
         <v>0.000383</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.422</v>
+        <v>0.501439</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1678,7 +1678,7 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0.418761</v>
+        <v>0.374202</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1721,7 +1721,7 @@
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.910829</v>
+        <v>0.8224089999999999</v>
       </c>
       <c r="H30" t="n">
         <v>1</v>
@@ -1764,7 +1764,7 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.283153</v>
+        <v>0.289541</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.303563</v>
+        <v>0.268176</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>0.289911</v>
+        <v>0.261741</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1893,7 +1893,7 @@
         <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>0.959917</v>
+        <v>0.841106</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1936,7 +1936,7 @@
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>0.366755</v>
+        <v>0.4654</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0.295009</v>
+        <v>0.233438</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0.408157</v>
+        <v>0.494738</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -2065,7 +2065,7 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.779174</v>
+        <v>0.621838</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>0.257542</v>
+        <v>0.335573</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -2151,7 +2151,7 @@
         <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>0.27604</v>
+        <v>0.253058</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -2194,7 +2194,7 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0.203761</v>
+        <v>0.339235</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0.271706</v>
+        <v>0.225896</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0.224813</v>
+        <v>0.269735</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -2320,10 +2320,10 @@
         <v>0.7279099999999999</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G44" t="n">
-        <v>0.405731</v>
+        <v>0.516379</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2363,10 +2363,10 @@
         <v>0.000901</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G45" t="n">
-        <v>0.447022</v>
+        <v>0.515996</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         <v>1</v>
       </c>
       <c r="G46" t="n">
-        <v>0.565922</v>
+        <v>0.610414</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2452,7 +2452,7 @@
         <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>0.220358</v>
+        <v>0.265395</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.425839</v>
+        <v>0.324694</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -2538,7 +2538,7 @@
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>0.751904</v>
+        <v>0.581406</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -2578,10 +2578,10 @@
         <v>4.1e-05</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>0.344112</v>
+        <v>0.509813</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
         <v>0</v>
       </c>
       <c r="G51" t="n">
-        <v>0.292491</v>
+        <v>0.391177</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -2667,7 +2667,7 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.991747</v>
+        <v>0.985271</v>
       </c>
       <c r="H52" t="n">
         <v>1</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>0.230934</v>
+        <v>0.277479</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0.782263</v>
+        <v>0.530013</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -2796,7 +2796,7 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.234769</v>
+        <v>0.440853</v>
       </c>
       <c r="H55" t="n">
         <v>1</v>
@@ -2839,7 +2839,7 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.230995</v>
+        <v>0.215748</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
         <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>0.277701</v>
+        <v>0.205978</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.438071</v>
+        <v>0.334198</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>0.448769</v>
+        <v>0.3731</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -3011,7 +3011,7 @@
         <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>0.481308</v>
+        <v>0.427781</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.976259</v>
+        <v>0.965128</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -3097,7 +3097,7 @@
         <v>0</v>
       </c>
       <c r="G62" t="n">
-        <v>0.304301</v>
+        <v>0.389164</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -3140,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.82931</v>
+        <v>0.937585</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -3180,10 +3180,10 @@
         <v>0.007799</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>0.369461</v>
+        <v>0.53234</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -3226,7 +3226,7 @@
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>0.590649</v>
+        <v>0.643171</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>0.163739</v>
+        <v>0.254923</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>0.277628</v>
+        <v>0.25758</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -3352,10 +3352,10 @@
         <v>0.29439</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>0.333961</v>
+        <v>0.515173</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -3398,7 +3398,7 @@
         <v>0</v>
       </c>
       <c r="G69" t="n">
-        <v>0.469159</v>
+        <v>0.449192</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -3441,7 +3441,7 @@
         <v>0</v>
       </c>
       <c r="G70" t="n">
-        <v>0.201947</v>
+        <v>0.205409</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -3481,10 +3481,10 @@
         <v>0.031844</v>
       </c>
       <c r="F71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G71" t="n">
-        <v>0.647432</v>
+        <v>0.452517</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="G72" t="n">
-        <v>0.207654</v>
+        <v>0.324147</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -3570,7 +3570,7 @@
         <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>0.243794</v>
+        <v>0.275692</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3613,7 +3613,7 @@
         <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>0.262657</v>
+        <v>0.326904</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -3653,10 +3653,10 @@
         <v>0.156134</v>
       </c>
       <c r="F75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>0.479225</v>
+        <v>0.522918</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -3696,10 +3696,10 @@
         <v>9e-06</v>
       </c>
       <c r="F76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G76" t="n">
-        <v>0.546617</v>
+        <v>0.382682</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3742,7 +3742,7 @@
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.98915</v>
+        <v>0.956695</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -3782,10 +3782,10 @@
         <v>0.011066</v>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0.468673</v>
+        <v>0.5131520000000001</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -3828,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="G79" t="n">
-        <v>0.239616</v>
+        <v>0.405604</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -3871,7 +3871,7 @@
         <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>0.268014</v>
+        <v>0.402072</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -3911,10 +3911,10 @@
         <v>4e-06</v>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0.459348</v>
+        <v>0.513436</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>0.337694</v>
+        <v>0.305616</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -4000,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="G83" t="n">
-        <v>0.359664</v>
+        <v>0.406576</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -4043,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="G84" t="n">
-        <v>0.136756</v>
+        <v>0.454249</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -4086,7 +4086,7 @@
         <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>0.214975</v>
+        <v>0.407651</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -4129,7 +4129,7 @@
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>0.6447850000000001</v>
+        <v>0.718455</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -4172,7 +4172,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>0.266052</v>
+        <v>0.306904</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -4215,7 +4215,7 @@
         <v>0</v>
       </c>
       <c r="G88" t="n">
-        <v>0.209906</v>
+        <v>0.389116</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -4258,7 +4258,7 @@
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>0.699195</v>
+        <v>0.9211549999999999</v>
       </c>
       <c r="H89" t="n">
         <v>1</v>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="G90" t="n">
-        <v>0.111619</v>
+        <v>0.139722</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -4344,7 +4344,7 @@
         <v>0</v>
       </c>
       <c r="G91" t="n">
-        <v>0.170612</v>
+        <v>0.202543</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -4387,7 +4387,7 @@
         <v>0</v>
       </c>
       <c r="G92" t="n">
-        <v>0.218835</v>
+        <v>0.42564</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -4430,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="G93" t="n">
-        <v>0.46086</v>
+        <v>0.469472</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -4473,7 +4473,7 @@
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>0.552247</v>
+        <v>0.570547</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -4513,10 +4513,10 @@
         <v>1.7e-05</v>
       </c>
       <c r="F95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
-        <v>0.559857</v>
+        <v>0.341798</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -4559,7 +4559,7 @@
         <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.447791</v>
+        <v>0.456936</v>
       </c>
       <c r="H96" t="n">
         <v>1</v>
@@ -4602,7 +4602,7 @@
         <v>0</v>
       </c>
       <c r="G97" t="n">
-        <v>0.190217</v>
+        <v>0.253891</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -4645,7 +4645,7 @@
         <v>1</v>
       </c>
       <c r="G98" t="n">
-        <v>0.619375</v>
+        <v>0.532802</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -4688,7 +4688,7 @@
         <v>1</v>
       </c>
       <c r="G99" t="n">
-        <v>0.949422</v>
+        <v>0.766768</v>
       </c>
       <c r="H99" t="n">
         <v>1</v>
@@ -4731,7 +4731,7 @@
         <v>0</v>
       </c>
       <c r="G100" t="n">
-        <v>0.283535</v>
+        <v>0.382906</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -4774,7 +4774,7 @@
         <v>1</v>
       </c>
       <c r="G101" t="n">
-        <v>0.935932</v>
+        <v>0.854755</v>
       </c>
       <c r="H101" t="n">
         <v>1</v>
@@ -4817,7 +4817,7 @@
         <v>1</v>
       </c>
       <c r="G102" t="n">
-        <v>0.892821</v>
+        <v>0.906581</v>
       </c>
       <c r="H102" t="n">
         <v>1</v>
@@ -4857,10 +4857,10 @@
         <v>0.016663</v>
       </c>
       <c r="F103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103" t="n">
-        <v>0.585287</v>
+        <v>0.43448</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -4903,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="G104" t="n">
-        <v>0.201366</v>
+        <v>0.319426</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="G105" t="n">
-        <v>0.388037</v>
+        <v>0.456114</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -4989,7 +4989,7 @@
         <v>0</v>
       </c>
       <c r="G106" t="n">
-        <v>0.098331</v>
+        <v>0.072281</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -5032,7 +5032,7 @@
         <v>0</v>
       </c>
       <c r="G107" t="n">
-        <v>0.153983</v>
+        <v>0.273738</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -5075,7 +5075,7 @@
         <v>1</v>
       </c>
       <c r="G108" t="n">
-        <v>0.918447</v>
+        <v>0.9623080000000001</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -5118,7 +5118,7 @@
         <v>0</v>
       </c>
       <c r="G109" t="n">
-        <v>0.195381</v>
+        <v>0.144542</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -5161,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="G110" t="n">
-        <v>0.789946</v>
+        <v>0.888321</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -5204,7 +5204,7 @@
         <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.089605</v>
+        <v>0.075132</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="G112" t="n">
-        <v>0.143331</v>
+        <v>0.221571</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="G113" t="n">
-        <v>0.279752</v>
+        <v>0.305346</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -5333,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="G114" t="n">
-        <v>0.170287</v>
+        <v>0.106879</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         <v>0</v>
       </c>
       <c r="G115" t="n">
-        <v>0.166215</v>
+        <v>0.136181</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>0</v>
       </c>
       <c r="G116" t="n">
-        <v>0.224979</v>
+        <v>0.199317</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -5462,7 +5462,7 @@
         <v>0</v>
       </c>
       <c r="G117" t="n">
-        <v>0.338352</v>
+        <v>0.292773</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="G118" t="n">
-        <v>0.176159</v>
+        <v>0.1127</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -5548,7 +5548,7 @@
         <v>1</v>
       </c>
       <c r="G119" t="n">
-        <v>0.597688</v>
+        <v>0.764267</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -5591,7 +5591,7 @@
         <v>0</v>
       </c>
       <c r="G120" t="n">
-        <v>0.12588</v>
+        <v>0.087662</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="G121" t="n">
-        <v>0.170039</v>
+        <v>0.206808</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -5677,7 +5677,7 @@
         <v>1</v>
       </c>
       <c r="G122" t="n">
-        <v>0.753846</v>
+        <v>0.863544</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -5720,7 +5720,7 @@
         <v>1</v>
       </c>
       <c r="G123" t="n">
-        <v>0.554965</v>
+        <v>0.741394</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="G124" t="n">
-        <v>0.283186</v>
+        <v>0.259747</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -5806,7 +5806,7 @@
         <v>0</v>
       </c>
       <c r="G125" t="n">
-        <v>0.163232</v>
+        <v>0.14438</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -5849,7 +5849,7 @@
         <v>0</v>
       </c>
       <c r="G126" t="n">
-        <v>0.219435</v>
+        <v>0.201181</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -5892,7 +5892,7 @@
         <v>0</v>
       </c>
       <c r="G127" t="n">
-        <v>0.219958</v>
+        <v>0.118599</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="G128" t="n">
-        <v>0.336516</v>
+        <v>0.263434</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -5978,7 +5978,7 @@
         <v>1</v>
       </c>
       <c r="G129" t="n">
-        <v>0.853716</v>
+        <v>0.918478</v>
       </c>
       <c r="H129" t="n">
         <v>1</v>
@@ -6021,7 +6021,7 @@
         <v>1</v>
       </c>
       <c r="G130" t="n">
-        <v>0.524622</v>
+        <v>0.602091</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -6064,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="G131" t="n">
-        <v>0.246053</v>
+        <v>0.181994</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -6107,7 +6107,7 @@
         <v>0</v>
       </c>
       <c r="G132" t="n">
-        <v>0.267408</v>
+        <v>0.186922</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="G133" t="n">
-        <v>0.314692</v>
+        <v>0.098854</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -6193,7 +6193,7 @@
         <v>1</v>
       </c>
       <c r="G134" t="n">
-        <v>0.640342</v>
+        <v>0.692091</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -6236,7 +6236,7 @@
         <v>0</v>
       </c>
       <c r="G135" t="n">
-        <v>0.187094</v>
+        <v>0.175282</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -6279,7 +6279,7 @@
         <v>0</v>
       </c>
       <c r="G136" t="n">
-        <v>0.15401</v>
+        <v>0.185292</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G137" t="n">
-        <v>0.195788</v>
+        <v>0.164411</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="G138" t="n">
-        <v>0.273424</v>
+        <v>0.270346</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>0</v>
       </c>
       <c r="G139" t="n">
-        <v>0.273295</v>
+        <v>0.266354</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="G140" t="n">
-        <v>0.198301</v>
+        <v>0.147711</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -6491,10 +6491,10 @@
         <v>0.152284</v>
       </c>
       <c r="F141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G141" t="n">
-        <v>0.489579</v>
+        <v>0.630718</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -6537,7 +6537,7 @@
         <v>0</v>
       </c>
       <c r="G142" t="n">
-        <v>0.325021</v>
+        <v>0.263075</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -6580,7 +6580,7 @@
         <v>0</v>
       </c>
       <c r="G143" t="n">
-        <v>0.23455</v>
+        <v>0.184105</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -6623,7 +6623,7 @@
         <v>0</v>
       </c>
       <c r="G144" t="n">
-        <v>0.321864</v>
+        <v>0.311005</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -6666,7 +6666,7 @@
         <v>0</v>
       </c>
       <c r="G145" t="n">
-        <v>0.301316</v>
+        <v>0.177255</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -6706,10 +6706,10 @@
         <v>0.04865</v>
       </c>
       <c r="F146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G146" t="n">
-        <v>0.440496</v>
+        <v>0.731026</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -6752,7 +6752,7 @@
         <v>0</v>
       </c>
       <c r="G147" t="n">
-        <v>0.290965</v>
+        <v>0.316535</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -6795,7 +6795,7 @@
         <v>0</v>
       </c>
       <c r="G148" t="n">
-        <v>0.122451</v>
+        <v>0.066582</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -6838,7 +6838,7 @@
         <v>0</v>
       </c>
       <c r="G149" t="n">
-        <v>0.29744</v>
+        <v>0.274553</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -6881,7 +6881,7 @@
         <v>0</v>
       </c>
       <c r="G150" t="n">
-        <v>0.166023</v>
+        <v>0.14751</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -6924,7 +6924,7 @@
         <v>0</v>
       </c>
       <c r="G151" t="n">
-        <v>0.27138</v>
+        <v>0.292774</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -6967,7 +6967,7 @@
         <v>1</v>
       </c>
       <c r="G152" t="n">
-        <v>0.997106</v>
+        <v>0.998549</v>
       </c>
       <c r="H152" t="n">
         <v>1</v>
@@ -7010,7 +7010,7 @@
         <v>0</v>
       </c>
       <c r="G153" t="n">
-        <v>0.167552</v>
+        <v>0.174671</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="G154" t="n">
-        <v>0.318376</v>
+        <v>0.22614</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -7096,7 +7096,7 @@
         <v>0</v>
       </c>
       <c r="G155" t="n">
-        <v>0.273762</v>
+        <v>0.119117</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -7139,7 +7139,7 @@
         <v>0</v>
       </c>
       <c r="G156" t="n">
-        <v>0.251878</v>
+        <v>0.264536</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -7182,7 +7182,7 @@
         <v>1</v>
       </c>
       <c r="G157" t="n">
-        <v>0.7706190000000001</v>
+        <v>0.725129</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -7225,7 +7225,7 @@
         <v>0</v>
       </c>
       <c r="G158" t="n">
-        <v>0.116457</v>
+        <v>0.118745</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -7268,7 +7268,7 @@
         <v>0</v>
       </c>
       <c r="G159" t="n">
-        <v>0.467721</v>
+        <v>0.453866</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -7311,7 +7311,7 @@
         <v>0</v>
       </c>
       <c r="G160" t="n">
-        <v>0.349608</v>
+        <v>0.176041</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -7354,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G161" t="n">
-        <v>0.200682</v>
+        <v>0.133694</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -7397,7 +7397,7 @@
         <v>0</v>
       </c>
       <c r="G162" t="n">
-        <v>0.253228</v>
+        <v>0.267512</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -7440,7 +7440,7 @@
         <v>0</v>
       </c>
       <c r="G163" t="n">
-        <v>0.459333</v>
+        <v>0.433554</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
         <v>0</v>
       </c>
       <c r="G164" t="n">
-        <v>0.240794</v>
+        <v>0.2355</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -7526,7 +7526,7 @@
         <v>0</v>
       </c>
       <c r="G165" t="n">
-        <v>0.351699</v>
+        <v>0.243487</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="G166" t="n">
-        <v>0.297482</v>
+        <v>0.227328</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="G167" t="n">
-        <v>0.345159</v>
+        <v>0.315507</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -7655,7 +7655,7 @@
         <v>1</v>
       </c>
       <c r="G168" t="n">
-        <v>0.926143</v>
+        <v>0.962716</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -7698,7 +7698,7 @@
         <v>0</v>
       </c>
       <c r="G169" t="n">
-        <v>0.302996</v>
+        <v>0.148503</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="G170" t="n">
-        <v>0.101608</v>
+        <v>0.06666900000000001</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="G171" t="n">
-        <v>0.158832</v>
+        <v>0.159113</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -7827,7 +7827,7 @@
         <v>0</v>
       </c>
       <c r="G172" t="n">
-        <v>0.307067</v>
+        <v>0.342079</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -7867,10 +7867,10 @@
         <v>0.000481</v>
       </c>
       <c r="F173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G173" t="n">
-        <v>0.620165</v>
+        <v>0.436696</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -7913,7 +7913,7 @@
         <v>0</v>
       </c>
       <c r="G174" t="n">
-        <v>0.115387</v>
+        <v>0.073348</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -7956,7 +7956,7 @@
         <v>0</v>
       </c>
       <c r="G175" t="n">
-        <v>0.177078</v>
+        <v>0.105712</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -7999,7 +7999,7 @@
         <v>0</v>
       </c>
       <c r="G176" t="n">
-        <v>0.218386</v>
+        <v>0.116723</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
         <v>0</v>
       </c>
       <c r="G177" t="n">
-        <v>0.114746</v>
+        <v>0.101704</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="G178" t="n">
-        <v>0.281926</v>
+        <v>0.123284</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -8128,7 +8128,7 @@
         <v>0</v>
       </c>
       <c r="G179" t="n">
-        <v>0.157806</v>
+        <v>0.073944</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -8171,7 +8171,7 @@
         <v>0</v>
       </c>
       <c r="G180" t="n">
-        <v>0.13308</v>
+        <v>0.051573</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -8214,7 +8214,7 @@
         <v>0</v>
       </c>
       <c r="G181" t="n">
-        <v>0.292948</v>
+        <v>0.150978</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>0</v>
       </c>
       <c r="G182" t="n">
-        <v>0.287305</v>
+        <v>0.165223</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -8300,7 +8300,7 @@
         <v>0</v>
       </c>
       <c r="G183" t="n">
-        <v>0.08533300000000001</v>
+        <v>0.04067</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -8343,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="G184" t="n">
-        <v>0.168566</v>
+        <v>0.163495</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -8386,7 +8386,7 @@
         <v>0</v>
       </c>
       <c r="G185" t="n">
-        <v>0.212551</v>
+        <v>0.186239</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="G186" t="n">
-        <v>0.224421</v>
+        <v>0.067423</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -8472,7 +8472,7 @@
         <v>0</v>
       </c>
       <c r="G187" t="n">
-        <v>0.169997</v>
+        <v>0.080899</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -8515,7 +8515,7 @@
         <v>0</v>
       </c>
       <c r="G188" t="n">
-        <v>0.156636</v>
+        <v>0.112151</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -8558,7 +8558,7 @@
         <v>0</v>
       </c>
       <c r="G189" t="n">
-        <v>0.196458</v>
+        <v>0.200639</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -8601,7 +8601,7 @@
         <v>0</v>
       </c>
       <c r="G190" t="n">
-        <v>0.315285</v>
+        <v>0.473581</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -8644,7 +8644,7 @@
         <v>1</v>
       </c>
       <c r="G191" t="n">
-        <v>0.709129</v>
+        <v>0.777891</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -8684,10 +8684,10 @@
         <v>0.00315</v>
       </c>
       <c r="F192" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G192" t="n">
-        <v>0.628983</v>
+        <v>0.448928</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -8730,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="G193" t="n">
-        <v>0.179718</v>
+        <v>0.310073</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -8773,7 +8773,7 @@
         <v>0</v>
       </c>
       <c r="G194" t="n">
-        <v>0.248934</v>
+        <v>0.243225</v>
       </c>
       <c r="H194" t="n">
         <v>1</v>
@@ -8816,7 +8816,7 @@
         <v>0</v>
       </c>
       <c r="G195" t="n">
-        <v>0.135503</v>
+        <v>0.169294</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -8859,7 +8859,7 @@
         <v>0</v>
       </c>
       <c r="G196" t="n">
-        <v>0.264269</v>
+        <v>0.169922</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -8902,7 +8902,7 @@
         <v>1</v>
       </c>
       <c r="G197" t="n">
-        <v>0.905559</v>
+        <v>0.90645</v>
       </c>
       <c r="H197" t="n">
         <v>1</v>
@@ -8945,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="G198" t="n">
-        <v>0.895979</v>
+        <v>0.967648</v>
       </c>
       <c r="H198" t="n">
         <v>1</v>
@@ -8988,7 +8988,7 @@
         <v>1</v>
       </c>
       <c r="G199" t="n">
-        <v>0.781073</v>
+        <v>0.930476</v>
       </c>
       <c r="H199" t="n">
         <v>1</v>
@@ -9031,7 +9031,7 @@
         <v>1</v>
       </c>
       <c r="G200" t="n">
-        <v>0.695684</v>
+        <v>0.78949</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="G201" t="n">
-        <v>0.257353</v>
+        <v>0.097717</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
